--- a/output/graficos_dimensiones/comunal_d_dep_a_2018_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2018_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:56</t>
+    <t xml:space="preserve">2026-09-10 01:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2018_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2018_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:07</t>
+    <t xml:space="preserve">2026-09-12 22:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2018_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2018_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:19</t>
+    <t xml:space="preserve">2026-09-23 23:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2018_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2018_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 23:47</t>
+    <t xml:space="preserve">2026-10-02 15:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2018_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2018_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:28</t>
+    <t xml:space="preserve">2026-10-05 15:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
